--- a/data/xlsx/aeosib--marine-engine-operation-and-maintenance.xlsx
+++ b/data/xlsx/aeosib--marine-engine-operation-and-maintenance.xlsx
@@ -136,7 +136,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -223,6 +223,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -623,7 +626,9 @@
       <c r="C16" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="27" t="n"/>
+      <c r="D16" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="27" t="n">
         <v>5</v>
       </c>
@@ -645,7 +650,9 @@
       <c r="C17" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="27" t="n"/>
+      <c r="D17" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="27" t="n">
         <v>5</v>
       </c>
@@ -667,7 +674,9 @@
       <c r="C18" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="D18" s="27" t="n"/>
+      <c r="D18" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="27" t="n">
         <v>10</v>
       </c>
@@ -689,7 +698,9 @@
       <c r="C19" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="27" t="n"/>
+      <c r="D19" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="27" t="n">
         <v>8</v>
       </c>
@@ -711,7 +722,9 @@
       <c r="C20" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="27" t="n"/>
+      <c r="D20" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="27" t="n">
         <v>8</v>
       </c>
@@ -733,7 +746,9 @@
       <c r="C21" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="27" t="n"/>
+      <c r="D21" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="27" t="n">
         <v>7</v>
       </c>
@@ -755,7 +770,9 @@
       <c r="C22" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="D22" s="27" t="n"/>
+      <c r="D22" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="27" t="n">
         <v>7</v>
       </c>
@@ -777,7 +794,9 @@
       <c r="C23" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="D23" s="27" t="n"/>
+      <c r="D23" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="27" t="n">
         <v>7</v>
       </c>
@@ -799,7 +818,9 @@
       <c r="C24" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="D24" s="27" t="n"/>
+      <c r="D24" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="27" t="n">
         <v>7</v>
       </c>
@@ -821,7 +842,9 @@
       <c r="C25" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="27" t="n"/>
+      <c r="D25" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="27" t="n">
         <v>6</v>
       </c>
@@ -843,7 +866,9 @@
       <c r="C26" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="27" t="n"/>
+      <c r="D26" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="27" t="n">
         <v>6</v>
       </c>
@@ -865,7 +890,9 @@
       <c r="C27" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="27" t="n"/>
+      <c r="D27" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="27" t="n">
         <v>6</v>
       </c>

--- a/data/xlsx/aeosib--marine-engine-operation-and-maintenance.xlsx
+++ b/data/xlsx/aeosib--marine-engine-operation-and-maintenance.xlsx
@@ -702,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="27" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F19" s="27">
         <f>IFERROR(MIN(C19,D19)*E19/C19,0)</f>
@@ -726,7 +726,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="27" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F20" s="27">
         <f>IFERROR(MIN(C20,D20)*E20/C20,0)</f>
@@ -774,7 +774,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F22" s="27">
         <f>IFERROR(MIN(C22,D22)*E22/C22,0)</f>
@@ -846,7 +846,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="27" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F25" s="27">
         <f>IFERROR(MIN(C25,D25)*E25/C25,0)</f>
@@ -870,7 +870,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="27" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F26" s="27">
         <f>IFERROR(MIN(C26,D26)*E26/C26,0)</f>
@@ -894,7 +894,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F27" s="27">
         <f>IFERROR(MIN(C27,D27)*E27/C27,0)</f>
